--- a/API Cost Calculator.xlsx
+++ b/API Cost Calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benji\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A8B2FD-69EF-431D-AC79-E69268D669D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0116B8-7B5E-434B-A3FF-79C07848038C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{246B3710-82D4-4E0C-91FF-DFF06D6F2205}"/>
   </bookViews>
@@ -1154,8 +1154,8 @@
         <v>51</v>
       </c>
       <c r="C28" s="3">
-        <f>0.05*SUM(C21:C26)</f>
-        <v>35.188911738390011</v>
+        <f>0.055*SUM(C21:C26)</f>
+        <v>38.707802912229013</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C29" s="2">
         <f>SUM(C21:C28)</f>
-        <v>738.96714650619026</v>
+        <v>742.4860376800292</v>
       </c>
     </row>
   </sheetData>
